--- a/reports/VerifyAI_Test_Results_305.xlsx
+++ b/reports/VerifyAI_Test_Results_305.xlsx
@@ -517,7 +517,7 @@
         <v>Generated Date</v>
       </c>
       <c r="B14" t="str">
-        <v>28/8/2026, 12:48:44 pm</v>
+        <v>28/8/2026, 1:11:28 pm</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
         <v>3ms</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-28T07:18:44.995Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="3">
@@ -613,10 +613,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G3" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="4">
@@ -639,10 +639,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G4" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="5">
@@ -665,10 +665,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G5" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="6">
@@ -694,7 +694,7 @@
         <v>2ms</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="7">
@@ -717,10 +717,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G7" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="8">
@@ -746,7 +746,7 @@
         <v>1ms</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="9">
@@ -772,7 +772,7 @@
         <v>2ms</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="10">
@@ -795,10 +795,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G10" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="11">
@@ -821,10 +821,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G11" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="12">
@@ -847,10 +847,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G12" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="13">
@@ -876,7 +876,7 @@
         <v>3ms</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="14">
@@ -899,10 +899,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G14" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="15">
@@ -925,10 +925,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G15" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="16">
@@ -954,7 +954,7 @@
         <v>3ms</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="17">
@@ -980,7 +980,7 @@
         <v>2ms</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="18">
@@ -1003,10 +1003,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G18" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="19">
@@ -1029,10 +1029,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G19" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="20">
@@ -1055,10 +1055,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G20" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="21">
@@ -1081,10 +1081,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G21" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="22">
@@ -1107,10 +1107,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G22" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="23">
@@ -1133,10 +1133,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G23" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="24">
@@ -1159,10 +1159,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G24" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="25">
@@ -1185,10 +1185,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G25" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="26">
@@ -1211,10 +1211,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G26" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="27">
@@ -1237,10 +1237,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G27" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="28">
@@ -1263,10 +1263,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G28" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="29">
@@ -1289,10 +1289,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G29" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="30">
@@ -1318,7 +1318,7 @@
         <v>3ms</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="31">
@@ -1341,10 +1341,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G31" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="32">
@@ -1370,7 +1370,7 @@
         <v>3ms</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="33">
@@ -1393,10 +1393,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G33" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="34">
@@ -1419,10 +1419,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G34" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="35">
@@ -1448,7 +1448,7 @@
         <v>3ms</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="36">
@@ -1471,10 +1471,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G36" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="37">
@@ -1497,10 +1497,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G37" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="38">
@@ -1523,10 +1523,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G38" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="39">
@@ -1549,10 +1549,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G39" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="40">
@@ -1578,7 +1578,7 @@
         <v>1ms</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="41">
@@ -1601,10 +1601,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G41" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="42">
@@ -1630,7 +1630,7 @@
         <v>1ms</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="43">
@@ -1653,10 +1653,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G43" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="44">
@@ -1679,10 +1679,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G44" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="45">
@@ -1705,10 +1705,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G45" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="46">
@@ -1731,10 +1731,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G46" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="47">
@@ -1760,7 +1760,7 @@
         <v>1ms</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="48">
@@ -1783,10 +1783,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G48" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="49">
@@ -1809,10 +1809,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G49" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="50">
@@ -1838,7 +1838,7 @@
         <v>3ms</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="51">
@@ -1861,10 +1861,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G51" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="52">
@@ -1887,10 +1887,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G52" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="53">
@@ -1913,10 +1913,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G53" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="54">
@@ -1939,10 +1939,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G54" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="55">
@@ -1965,10 +1965,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G55" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="56">
@@ -1994,7 +1994,7 @@
         <v>4ms</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="57">
@@ -2020,7 +2020,7 @@
         <v>1ms</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="58">
@@ -2046,7 +2046,7 @@
         <v>4ms</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="59">
@@ -2069,10 +2069,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G59" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="60">
@@ -2098,7 +2098,7 @@
         <v>1ms</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="61">
@@ -2121,10 +2121,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G61" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="62">
@@ -2147,10 +2147,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G62" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="63">
@@ -2173,10 +2173,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G63" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="64">
@@ -2199,10 +2199,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G64" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="65">
@@ -2225,10 +2225,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G65" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="66">
@@ -2254,7 +2254,7 @@
         <v>3ms</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="67">
@@ -2277,10 +2277,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G67" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="68">
@@ -2303,10 +2303,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G68" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="69">
@@ -2329,10 +2329,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G69" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="70">
@@ -2355,10 +2355,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G70" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="71">
@@ -2381,10 +2381,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G71" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="72">
@@ -2410,7 +2410,7 @@
         <v>4ms</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="73">
@@ -2436,7 +2436,7 @@
         <v>2ms</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="74">
@@ -2459,10 +2459,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G74" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="75">
@@ -2485,10 +2485,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G75" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="76">
@@ -2511,10 +2511,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G76" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="77">
@@ -2540,7 +2540,7 @@
         <v>3ms</v>
       </c>
       <c r="H77" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="78">
@@ -2566,7 +2566,7 @@
         <v>3ms</v>
       </c>
       <c r="H78" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="79">
@@ -2589,10 +2589,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G79" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H79" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="80">
@@ -2615,10 +2615,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G80" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H80" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="81">
@@ -2641,10 +2641,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G81" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H81" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="82">
@@ -2670,7 +2670,7 @@
         <v>1ms</v>
       </c>
       <c r="H82" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="83">
@@ -2693,10 +2693,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G83" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H83" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="84">
@@ -2719,10 +2719,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G84" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H84" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="85">
@@ -2745,10 +2745,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G85" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H85" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="86">
@@ -2771,10 +2771,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G86" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H86" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="87">
@@ -2800,7 +2800,7 @@
         <v>3ms</v>
       </c>
       <c r="H87" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="88">
@@ -2823,10 +2823,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G88" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H88" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="89">
@@ -2849,10 +2849,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G89" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H89" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="90">
@@ -2875,10 +2875,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G90" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H90" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="91">
@@ -2904,7 +2904,7 @@
         <v>3ms</v>
       </c>
       <c r="H91" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="92">
@@ -2930,7 +2930,7 @@
         <v>4ms</v>
       </c>
       <c r="H92" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="93">
@@ -2956,7 +2956,7 @@
         <v>2ms</v>
       </c>
       <c r="H93" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="94">
@@ -2979,10 +2979,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G94" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H94" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="95">
@@ -3005,10 +3005,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G95" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H95" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="96">
@@ -3031,10 +3031,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G96" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H96" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="97">
@@ -3057,10 +3057,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G97" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H97" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="98">
@@ -3083,10 +3083,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G98" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H98" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="99">
@@ -3109,10 +3109,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G99" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H99" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="100">
@@ -3135,10 +3135,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G100" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H100" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="101">
@@ -3164,7 +3164,7 @@
         <v>2ms</v>
       </c>
       <c r="H101" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="102">
@@ -3187,10 +3187,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G102" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H102" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="103">
@@ -3213,10 +3213,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G103" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H103" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="104">
@@ -3239,10 +3239,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G104" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H104" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="105">
@@ -3265,10 +3265,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G105" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H105" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="106">
@@ -3294,7 +3294,7 @@
         <v>2ms</v>
       </c>
       <c r="H106" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="107">
@@ -3317,10 +3317,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G107" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H107" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="108">
@@ -3343,10 +3343,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G108" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H108" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="109">
@@ -3369,10 +3369,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G109" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H109" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="110">
@@ -3395,10 +3395,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G110" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H110" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="111">
@@ -3421,10 +3421,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G111" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H111" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="112">
@@ -3450,7 +3450,7 @@
         <v>2ms</v>
       </c>
       <c r="H112" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="113">
@@ -3473,10 +3473,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G113" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H113" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="114">
@@ -3499,10 +3499,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G114" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H114" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="115">
@@ -3525,10 +3525,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G115" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H115" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="116">
@@ -3551,10 +3551,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G116" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H116" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="117">
@@ -3577,10 +3577,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G117" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H117" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="118">
@@ -3603,10 +3603,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G118" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H118" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="119">
@@ -3632,7 +3632,7 @@
         <v>1ms</v>
       </c>
       <c r="H119" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="120">
@@ -3655,10 +3655,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G120" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H120" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="121">
@@ -3681,10 +3681,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G121" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H121" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="122">
@@ -3707,10 +3707,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G122" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H122" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="123">
@@ -3733,10 +3733,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G123" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H123" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="124">
@@ -3762,7 +3762,7 @@
         <v>3ms</v>
       </c>
       <c r="H124" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="125">
@@ -3788,7 +3788,7 @@
         <v>4ms</v>
       </c>
       <c r="H125" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="126">
@@ -3814,7 +3814,7 @@
         <v>1ms</v>
       </c>
       <c r="H126" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="127">
@@ -3837,10 +3837,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G127" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H127" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="128">
@@ -3863,10 +3863,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G128" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H128" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="129">
@@ -3889,10 +3889,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G129" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H129" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="130">
@@ -3915,10 +3915,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G130" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H130" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="131">
@@ -3944,7 +3944,7 @@
         <v>3ms</v>
       </c>
       <c r="H131" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="132">
@@ -3967,10 +3967,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G132" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H132" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="133">
@@ -3993,10 +3993,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G133" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H133" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="134">
@@ -4022,7 +4022,7 @@
         <v>3ms</v>
       </c>
       <c r="H134" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="135">
@@ -4045,10 +4045,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G135" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H135" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="136">
@@ -4071,10 +4071,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G136" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H136" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="137">
@@ -4100,7 +4100,7 @@
         <v>2ms</v>
       </c>
       <c r="H137" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="138">
@@ -4123,10 +4123,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G138" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H138" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="139">
@@ -4149,10 +4149,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G139" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H139" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="140">
@@ -4178,7 +4178,7 @@
         <v>3ms</v>
       </c>
       <c r="H140" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="141">
@@ -4204,7 +4204,7 @@
         <v>3ms</v>
       </c>
       <c r="H141" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="142">
@@ -4227,10 +4227,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G142" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H142" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="143">
@@ -4253,10 +4253,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G143" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H143" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="144">
@@ -4279,10 +4279,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G144" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H144" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="145">
@@ -4305,10 +4305,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G145" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H145" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="146">
@@ -4331,10 +4331,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G146" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H146" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="147">
@@ -4360,7 +4360,7 @@
         <v>3ms</v>
       </c>
       <c r="H147" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="148">
@@ -4383,10 +4383,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G148" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H148" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="149">
@@ -4412,7 +4412,7 @@
         <v>3ms</v>
       </c>
       <c r="H149" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="150">
@@ -4438,7 +4438,7 @@
         <v>4ms</v>
       </c>
       <c r="H150" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="151">
@@ -4461,10 +4461,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G151" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H151" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="152">
@@ -4487,10 +4487,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G152" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H152" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="153">
@@ -4516,7 +4516,7 @@
         <v>1ms</v>
       </c>
       <c r="H153" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="154">
@@ -4539,10 +4539,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G154" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H154" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="155">
@@ -4568,7 +4568,7 @@
         <v>4ms</v>
       </c>
       <c r="H155" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="156">
@@ -4591,10 +4591,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G156" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H156" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="157">
@@ -4617,10 +4617,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G157" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H157" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="158">
@@ -4643,10 +4643,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G158" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H158" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="159">
@@ -4669,10 +4669,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G159" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H159" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="160">
@@ -4695,10 +4695,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G160" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H160" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="161">
@@ -4721,10 +4721,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G161" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H161" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="162">
@@ -4747,10 +4747,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G162" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H162" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="163">
@@ -4773,10 +4773,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G163" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H163" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="164">
@@ -4799,10 +4799,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G164" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H164" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="165">
@@ -4828,7 +4828,7 @@
         <v>3ms</v>
       </c>
       <c r="H165" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="166">
@@ -4851,10 +4851,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G166" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H166" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="167">
@@ -4880,7 +4880,7 @@
         <v>2ms</v>
       </c>
       <c r="H167" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="168">
@@ -4903,10 +4903,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G168" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H168" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="169">
@@ -4932,7 +4932,7 @@
         <v>4ms</v>
       </c>
       <c r="H169" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="170">
@@ -4958,7 +4958,7 @@
         <v>3ms</v>
       </c>
       <c r="H170" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="171">
@@ -4981,10 +4981,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G171" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H171" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="172">
@@ -5007,10 +5007,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G172" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H172" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="173">
@@ -5033,10 +5033,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G173" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H173" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="174">
@@ -5059,10 +5059,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G174" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H174" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="175">
@@ -5088,7 +5088,7 @@
         <v>3ms</v>
       </c>
       <c r="H175" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="176">
@@ -5114,7 +5114,7 @@
         <v>3ms</v>
       </c>
       <c r="H176" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="177">
@@ -5140,7 +5140,7 @@
         <v>1ms</v>
       </c>
       <c r="H177" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="178">
@@ -5163,10 +5163,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G178" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H178" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="179">
@@ -5189,10 +5189,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G179" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H179" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="180">
@@ -5218,7 +5218,7 @@
         <v>1ms</v>
       </c>
       <c r="H180" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="181">
@@ -5244,7 +5244,7 @@
         <v>1ms</v>
       </c>
       <c r="H181" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="182">
@@ -5267,10 +5267,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G182" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H182" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="183">
@@ -5293,10 +5293,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G183" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H183" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="184">
@@ -5319,10 +5319,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G184" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H184" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="185">
@@ -5345,10 +5345,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G185" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H185" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="186">
@@ -5371,10 +5371,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G186" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H186" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="187">
@@ -5397,10 +5397,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G187" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H187" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="188">
@@ -5423,10 +5423,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G188" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H188" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="189">
@@ -5449,10 +5449,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G189" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H189" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="190">
@@ -5478,7 +5478,7 @@
         <v>1ms</v>
       </c>
       <c r="H190" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="191">
@@ -5501,10 +5501,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G191" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H191" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="192">
@@ -5527,10 +5527,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G192" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H192" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="193">
@@ -5553,10 +5553,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G193" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H193" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="194">
@@ -5582,7 +5582,7 @@
         <v>3ms</v>
       </c>
       <c r="H194" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="195">
@@ -5605,10 +5605,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G195" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H195" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="196">
@@ -5634,7 +5634,7 @@
         <v>4ms</v>
       </c>
       <c r="H196" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="197">
@@ -5657,10 +5657,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G197" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H197" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="198">
@@ -5686,7 +5686,7 @@
         <v>4ms</v>
       </c>
       <c r="H198" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="199">
@@ -5709,10 +5709,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G199" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H199" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="200">
@@ -5738,7 +5738,7 @@
         <v>1ms</v>
       </c>
       <c r="H200" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="201">
@@ -5761,10 +5761,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G201" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H201" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="202">
@@ -5787,10 +5787,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G202" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H202" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="203">
@@ -5813,10 +5813,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G203" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H203" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="204">
@@ -5839,10 +5839,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G204" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H204" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="205">
@@ -5868,7 +5868,7 @@
         <v>4ms</v>
       </c>
       <c r="H205" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="206">
@@ -5891,10 +5891,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G206" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H206" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="207">
@@ -5917,10 +5917,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G207" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H207" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="208">
@@ -5946,7 +5946,7 @@
         <v>4ms</v>
       </c>
       <c r="H208" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="209">
@@ -5969,10 +5969,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G209" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H209" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="210">
@@ -5995,10 +5995,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G210" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H210" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="211">
@@ -6021,10 +6021,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G211" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H211" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="212">
@@ -6047,10 +6047,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G212" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H212" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="213">
@@ -6073,10 +6073,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G213" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H213" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="214">
@@ -6099,10 +6099,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G214" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H214" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="215">
@@ -6128,7 +6128,7 @@
         <v>1ms</v>
       </c>
       <c r="H215" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="216">
@@ -6151,10 +6151,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G216" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H216" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="217">
@@ -6177,10 +6177,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G217" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H217" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="218">
@@ -6206,7 +6206,7 @@
         <v>1ms</v>
       </c>
       <c r="H218" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="219">
@@ -6232,7 +6232,7 @@
         <v>1ms</v>
       </c>
       <c r="H219" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="220">
@@ -6258,7 +6258,7 @@
         <v>4ms</v>
       </c>
       <c r="H220" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="221">
@@ -6281,10 +6281,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G221" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H221" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="222">
@@ -6307,10 +6307,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G222" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H222" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="223">
@@ -6333,10 +6333,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G223" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H223" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="224">
@@ -6359,10 +6359,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G224" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H224" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="225">
@@ -6385,10 +6385,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G225" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H225" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="226">
@@ -6411,10 +6411,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G226" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H226" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="227">
@@ -6437,10 +6437,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G227" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H227" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="228">
@@ -6463,10 +6463,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G228" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H228" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="229">
@@ -6489,10 +6489,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G229" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H229" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="230">
@@ -6518,7 +6518,7 @@
         <v>2ms</v>
       </c>
       <c r="H230" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="231">
@@ -6541,10 +6541,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G231" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H231" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="232">
@@ -6570,7 +6570,7 @@
         <v>3ms</v>
       </c>
       <c r="H232" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="233">
@@ -6593,10 +6593,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G233" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H233" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="234">
@@ -6622,7 +6622,7 @@
         <v>3ms</v>
       </c>
       <c r="H234" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="235">
@@ -6645,10 +6645,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G235" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H235" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="236">
@@ -6671,10 +6671,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G236" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H236" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="237">
@@ -6700,7 +6700,7 @@
         <v>2ms</v>
       </c>
       <c r="H237" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="238">
@@ -6726,7 +6726,7 @@
         <v>4ms</v>
       </c>
       <c r="H238" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="239">
@@ -6749,10 +6749,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G239" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H239" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="240">
@@ -6778,7 +6778,7 @@
         <v>1ms</v>
       </c>
       <c r="H240" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="241">
@@ -6801,10 +6801,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G241" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H241" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="242">
@@ -6830,7 +6830,7 @@
         <v>3ms</v>
       </c>
       <c r="H242" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="243">
@@ -6853,10 +6853,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G243" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H243" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="244">
@@ -6882,7 +6882,7 @@
         <v>3ms</v>
       </c>
       <c r="H244" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="245">
@@ -6905,10 +6905,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G245" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H245" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="246">
@@ -6931,10 +6931,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G246" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H246" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="247">
@@ -6957,10 +6957,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G247" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H247" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="248">
@@ -6983,10 +6983,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G248" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H248" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="249">
@@ -7012,7 +7012,7 @@
         <v>4ms</v>
       </c>
       <c r="H249" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="250">
@@ -7035,10 +7035,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G250" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H250" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="251">
@@ -7061,10 +7061,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G251" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H251" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="252">
@@ -7087,10 +7087,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G252" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H252" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="253">
@@ -7113,10 +7113,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G253" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H253" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="254">
@@ -7139,10 +7139,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G254" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H254" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="255">
@@ -7165,10 +7165,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G255" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H255" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="256">
@@ -7191,10 +7191,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G256" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H256" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="257">
@@ -7217,10 +7217,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G257" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H257" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="258">
@@ -7246,7 +7246,7 @@
         <v>1ms</v>
       </c>
       <c r="H258" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="259">
@@ -7269,10 +7269,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G259" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H259" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="260">
@@ -7298,7 +7298,7 @@
         <v>3ms</v>
       </c>
       <c r="H260" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="261">
@@ -7324,7 +7324,7 @@
         <v>4ms</v>
       </c>
       <c r="H261" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="262">
@@ -7350,7 +7350,7 @@
         <v>2ms</v>
       </c>
       <c r="H262" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="263">
@@ -7373,10 +7373,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G263" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H263" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="264">
@@ -7399,10 +7399,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G264" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H264" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="265">
@@ -7428,7 +7428,7 @@
         <v>1ms</v>
       </c>
       <c r="H265" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="266">
@@ -7451,10 +7451,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G266" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H266" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="267">
@@ -7480,7 +7480,7 @@
         <v>2ms</v>
       </c>
       <c r="H267" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="268">
@@ -7506,7 +7506,7 @@
         <v>3ms</v>
       </c>
       <c r="H268" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="269">
@@ -7529,10 +7529,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G269" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H269" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="270">
@@ -7555,10 +7555,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G270" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H270" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="271">
@@ -7581,10 +7581,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G271" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H271" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="272">
@@ -7607,10 +7607,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G272" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H272" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="273">
@@ -7633,10 +7633,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G273" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H273" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="274">
@@ -7659,10 +7659,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G274" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H274" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="275">
@@ -7685,10 +7685,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G275" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H275" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="276">
@@ -7711,10 +7711,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G276" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H276" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="277">
@@ -7737,10 +7737,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G277" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H277" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="278">
@@ -7763,10 +7763,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G278" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H278" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="279">
@@ -7792,7 +7792,7 @@
         <v>1ms</v>
       </c>
       <c r="H279" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="280">
@@ -7815,10 +7815,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G280" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H280" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="281">
@@ -7841,10 +7841,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G281" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H281" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="282">
@@ -7867,10 +7867,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G282" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H282" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="283">
@@ -7896,7 +7896,7 @@
         <v>4ms</v>
       </c>
       <c r="H283" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="284">
@@ -7919,10 +7919,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G284" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H284" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="285">
@@ -7945,10 +7945,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G285" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H285" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="286">
@@ -7971,10 +7971,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G286" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H286" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="287">
@@ -8000,7 +8000,7 @@
         <v>2ms</v>
       </c>
       <c r="H287" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="288">
@@ -8026,7 +8026,7 @@
         <v>4ms</v>
       </c>
       <c r="H288" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="289">
@@ -8052,7 +8052,7 @@
         <v>2ms</v>
       </c>
       <c r="H289" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="290">
@@ -8075,10 +8075,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G290" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H290" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="291">
@@ -8104,7 +8104,7 @@
         <v>4ms</v>
       </c>
       <c r="H291" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="292">
@@ -8127,10 +8127,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G292" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H292" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="293">
@@ -8153,10 +8153,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G293" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H293" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="294">
@@ -8179,10 +8179,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G294" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H294" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="295">
@@ -8208,7 +8208,7 @@
         <v>4ms</v>
       </c>
       <c r="H295" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="296">
@@ -8234,7 +8234,7 @@
         <v>1ms</v>
       </c>
       <c r="H296" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="297">
@@ -8260,7 +8260,7 @@
         <v>2ms</v>
       </c>
       <c r="H297" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="298">
@@ -8283,10 +8283,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G298" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H298" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="299">
@@ -8309,10 +8309,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G299" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H299" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="300">
@@ -8335,10 +8335,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G300" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H300" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="301">
@@ -8361,10 +8361,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G301" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H301" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="302">
@@ -8387,10 +8387,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G302" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H302" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="303">
@@ -8413,10 +8413,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G303" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H303" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="304">
@@ -8442,7 +8442,7 @@
         <v>3ms</v>
       </c>
       <c r="H304" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="305">
@@ -8465,10 +8465,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G305" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H305" t="str">
-        <v>2026-08-28T07:18:44.999Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="306">
@@ -8491,10 +8491,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G306" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H306" t="str">
-        <v>2026-08-28T07:18:44.999Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
   </sheetData>
@@ -8567,7 +8567,7 @@
         <v>3ms</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-28T07:18:44.995Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="3">
@@ -8590,10 +8590,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G3" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="4">
@@ -8616,10 +8616,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G4" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="5">
@@ -8642,10 +8642,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G5" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="6">
@@ -8671,7 +8671,7 @@
         <v>2ms</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="7">
@@ -8694,10 +8694,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G7" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="8">
@@ -8723,7 +8723,7 @@
         <v>1ms</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="9">
@@ -8749,7 +8749,7 @@
         <v>2ms</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="10">
@@ -8772,10 +8772,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G10" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="11">
@@ -8798,10 +8798,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G11" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="12">
@@ -8824,10 +8824,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G12" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="13">
@@ -8853,7 +8853,7 @@
         <v>3ms</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="14">
@@ -8876,10 +8876,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G14" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="15">
@@ -8902,10 +8902,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G15" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="16">
@@ -8931,7 +8931,7 @@
         <v>3ms</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="17">
@@ -8957,7 +8957,7 @@
         <v>2ms</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="18">
@@ -8980,10 +8980,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G18" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="19">
@@ -9006,10 +9006,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G19" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="20">
@@ -9032,10 +9032,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G20" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="21">
@@ -9058,10 +9058,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G21" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="22">
@@ -9084,10 +9084,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G22" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="23">
@@ -9110,10 +9110,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G23" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="24">
@@ -9136,10 +9136,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G24" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="25">
@@ -9162,10 +9162,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G25" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="26">
@@ -9188,10 +9188,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G26" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="27">
@@ -9214,10 +9214,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G27" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="28">
@@ -9240,10 +9240,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G28" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="29">
@@ -9266,10 +9266,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G29" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="30">
@@ -9295,7 +9295,7 @@
         <v>3ms</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="31">
@@ -9318,10 +9318,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G31" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="32">
@@ -9347,7 +9347,7 @@
         <v>3ms</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="33">
@@ -9370,10 +9370,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G33" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="34">
@@ -9396,10 +9396,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G34" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="35">
@@ -9425,7 +9425,7 @@
         <v>3ms</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="36">
@@ -9448,10 +9448,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G36" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="37">
@@ -9474,10 +9474,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G37" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="38">
@@ -9500,10 +9500,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G38" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="39">
@@ -9526,10 +9526,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G39" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="40">
@@ -9555,7 +9555,7 @@
         <v>1ms</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="41">
@@ -9578,10 +9578,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G41" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="42">
@@ -9607,7 +9607,7 @@
         <v>1ms</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="43">
@@ -9630,10 +9630,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G43" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="44">
@@ -9656,10 +9656,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G44" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="45">
@@ -9682,10 +9682,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G45" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="46">
@@ -9708,10 +9708,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G46" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="47">
@@ -9737,7 +9737,7 @@
         <v>1ms</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="48">
@@ -9760,10 +9760,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G48" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="49">
@@ -9786,10 +9786,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G49" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="50">
@@ -9815,7 +9815,7 @@
         <v>3ms</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="51">
@@ -9838,10 +9838,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G51" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="52">
@@ -9864,10 +9864,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G52" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="53">
@@ -9890,10 +9890,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G53" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="54">
@@ -9916,10 +9916,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G54" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="55">
@@ -9942,10 +9942,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G55" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="56">
@@ -9971,7 +9971,7 @@
         <v>4ms</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="57">
@@ -9997,7 +9997,7 @@
         <v>1ms</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="58">
@@ -10023,7 +10023,7 @@
         <v>4ms</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="59">
@@ -10046,10 +10046,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G59" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="60">
@@ -10075,7 +10075,7 @@
         <v>1ms</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="61">
@@ -10098,10 +10098,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G61" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="62">
@@ -10124,10 +10124,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G62" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="63">
@@ -10150,10 +10150,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G63" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="64">
@@ -10176,10 +10176,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G64" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="65">
@@ -10202,10 +10202,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G65" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="66">
@@ -10231,7 +10231,7 @@
         <v>3ms</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="67">
@@ -10254,10 +10254,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G67" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="68">
@@ -10280,10 +10280,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G68" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="69">
@@ -10306,10 +10306,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G69" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="70">
@@ -10332,10 +10332,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G70" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.224Z</v>
       </c>
     </row>
     <row r="71">
@@ -10358,10 +10358,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G71" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="72">
@@ -10387,7 +10387,7 @@
         <v>4ms</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="73">
@@ -10413,7 +10413,7 @@
         <v>2ms</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="74">
@@ -10436,10 +10436,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G74" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="75">
@@ -10462,10 +10462,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G75" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="76">
@@ -10488,10 +10488,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G76" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="77">
@@ -10517,7 +10517,7 @@
         <v>3ms</v>
       </c>
       <c r="H77" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="78">
@@ -10543,7 +10543,7 @@
         <v>3ms</v>
       </c>
       <c r="H78" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="79">
@@ -10566,10 +10566,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G79" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H79" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="80">
@@ -10592,10 +10592,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G80" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H80" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="81">
@@ -10618,10 +10618,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G81" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H81" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
   </sheetData>
@@ -10694,7 +10694,7 @@
         <v>1ms</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="3">
@@ -10717,10 +10717,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G3" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="4">
@@ -10743,10 +10743,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G4" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="5">
@@ -10769,10 +10769,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G5" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="6">
@@ -10795,10 +10795,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G6" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="7">
@@ -10824,7 +10824,7 @@
         <v>3ms</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="8">
@@ -10847,10 +10847,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G8" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="9">
@@ -10873,10 +10873,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G9" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="10">
@@ -10899,10 +10899,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G10" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="11">
@@ -10928,7 +10928,7 @@
         <v>3ms</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="12">
@@ -10954,7 +10954,7 @@
         <v>4ms</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="13">
@@ -10980,7 +10980,7 @@
         <v>2ms</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="14">
@@ -11003,10 +11003,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G14" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="15">
@@ -11029,10 +11029,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G15" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="16">
@@ -11055,10 +11055,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G16" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="17">
@@ -11081,10 +11081,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G17" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="18">
@@ -11107,10 +11107,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G18" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="19">
@@ -11133,10 +11133,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G19" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="20">
@@ -11159,10 +11159,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G20" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="21">
@@ -11188,7 +11188,7 @@
         <v>2ms</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="22">
@@ -11211,10 +11211,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G22" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="23">
@@ -11237,10 +11237,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G23" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="24">
@@ -11263,10 +11263,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G24" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="25">
@@ -11289,10 +11289,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G25" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="26">
@@ -11318,7 +11318,7 @@
         <v>2ms</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="27">
@@ -11341,10 +11341,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G27" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="28">
@@ -11367,10 +11367,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G28" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="29">
@@ -11393,10 +11393,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G29" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="30">
@@ -11419,10 +11419,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G30" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="31">
@@ -11445,10 +11445,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G31" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="32">
@@ -11474,7 +11474,7 @@
         <v>2ms</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="33">
@@ -11497,10 +11497,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G33" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="34">
@@ -11523,10 +11523,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G34" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="35">
@@ -11549,10 +11549,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G35" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="36">
@@ -11575,10 +11575,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G36" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="37">
@@ -11601,10 +11601,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G37" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="38">
@@ -11627,10 +11627,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G38" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="39">
@@ -11656,7 +11656,7 @@
         <v>1ms</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="40">
@@ -11679,10 +11679,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G40" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="41">
@@ -11705,10 +11705,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G41" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="42">
@@ -11731,10 +11731,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G42" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="43">
@@ -11757,10 +11757,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G43" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="44">
@@ -11786,7 +11786,7 @@
         <v>3ms</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="45">
@@ -11812,7 +11812,7 @@
         <v>4ms</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="46">
@@ -11838,7 +11838,7 @@
         <v>1ms</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="47">
@@ -11861,10 +11861,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G47" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="48">
@@ -11887,10 +11887,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G48" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="49">
@@ -11913,10 +11913,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G49" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="50">
@@ -11939,10 +11939,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G50" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="51">
@@ -11968,7 +11968,7 @@
         <v>3ms</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="52">
@@ -11991,10 +11991,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G52" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="53">
@@ -12017,10 +12017,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G53" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="54">
@@ -12046,7 +12046,7 @@
         <v>3ms</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="55">
@@ -12069,10 +12069,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G55" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="56">
@@ -12095,10 +12095,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G56" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="57">
@@ -12124,7 +12124,7 @@
         <v>2ms</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="58">
@@ -12147,10 +12147,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G58" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="59">
@@ -12173,10 +12173,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G59" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="60">
@@ -12202,7 +12202,7 @@
         <v>3ms</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="61">
@@ -12228,7 +12228,7 @@
         <v>3ms</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="62">
@@ -12251,10 +12251,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G62" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="63">
@@ -12277,10 +12277,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G63" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="64">
@@ -12303,10 +12303,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G64" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="65">
@@ -12329,10 +12329,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G65" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="66">
@@ -12355,10 +12355,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G66" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="67">
@@ -12384,7 +12384,7 @@
         <v>3ms</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="68">
@@ -12407,10 +12407,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G68" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="69">
@@ -12436,7 +12436,7 @@
         <v>3ms</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="70">
@@ -12462,7 +12462,7 @@
         <v>4ms</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="71">
@@ -12485,10 +12485,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G71" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="72">
@@ -12511,10 +12511,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G72" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="73">
@@ -12540,7 +12540,7 @@
         <v>1ms</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="74">
@@ -12563,10 +12563,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G74" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="75">
@@ -12592,7 +12592,7 @@
         <v>4ms</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
     <row r="76">
@@ -12615,10 +12615,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G76" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-28T07:18:44.996Z</v>
+        <v>2026-08-28T07:41:28.225Z</v>
       </c>
     </row>
   </sheetData>
@@ -12688,10 +12688,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G2" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="3">
@@ -12714,10 +12714,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G3" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="4">
@@ -12740,10 +12740,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G4" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="5">
@@ -12766,10 +12766,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G5" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="6">
@@ -12792,10 +12792,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G6" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="7">
@@ -12818,10 +12818,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G7" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="8">
@@ -12844,10 +12844,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G8" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="9">
@@ -12870,10 +12870,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G9" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="10">
@@ -12899,7 +12899,7 @@
         <v>3ms</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="11">
@@ -12922,10 +12922,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G11" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="12">
@@ -12951,7 +12951,7 @@
         <v>2ms</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="13">
@@ -12974,10 +12974,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G13" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="14">
@@ -13003,7 +13003,7 @@
         <v>4ms</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="15">
@@ -13029,7 +13029,7 @@
         <v>3ms</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="16">
@@ -13052,10 +13052,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G16" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="17">
@@ -13078,10 +13078,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G17" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="18">
@@ -13104,10 +13104,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G18" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="19">
@@ -13130,10 +13130,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G19" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="20">
@@ -13159,7 +13159,7 @@
         <v>3ms</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="21">
@@ -13185,7 +13185,7 @@
         <v>3ms</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="22">
@@ -13211,7 +13211,7 @@
         <v>1ms</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="23">
@@ -13234,10 +13234,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G23" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="24">
@@ -13260,10 +13260,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G24" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="25">
@@ -13289,7 +13289,7 @@
         <v>1ms</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="26">
@@ -13315,7 +13315,7 @@
         <v>1ms</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="27">
@@ -13338,10 +13338,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G27" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="28">
@@ -13364,10 +13364,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G28" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="29">
@@ -13390,10 +13390,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G29" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="30">
@@ -13416,10 +13416,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G30" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="31">
@@ -13442,10 +13442,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G31" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="32">
@@ -13468,10 +13468,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G32" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="33">
@@ -13494,10 +13494,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G33" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="34">
@@ -13520,10 +13520,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G34" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="35">
@@ -13549,7 +13549,7 @@
         <v>1ms</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="36">
@@ -13572,10 +13572,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G36" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="37">
@@ -13598,10 +13598,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G37" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="38">
@@ -13624,10 +13624,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G38" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="39">
@@ -13653,7 +13653,7 @@
         <v>3ms</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="40">
@@ -13676,10 +13676,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G40" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="41">
@@ -13705,7 +13705,7 @@
         <v>4ms</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="42">
@@ -13728,10 +13728,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G42" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="43">
@@ -13757,7 +13757,7 @@
         <v>4ms</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="44">
@@ -13780,10 +13780,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G44" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="45">
@@ -13809,7 +13809,7 @@
         <v>1ms</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="46">
@@ -13832,10 +13832,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G46" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="47">
@@ -13858,10 +13858,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G47" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="48">
@@ -13884,10 +13884,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G48" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="49">
@@ -13910,10 +13910,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G49" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="50">
@@ -13939,7 +13939,7 @@
         <v>4ms</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="51">
@@ -13962,10 +13962,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G51" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="52">
@@ -13988,10 +13988,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G52" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="53">
@@ -14017,7 +14017,7 @@
         <v>4ms</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="54">
@@ -14040,10 +14040,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G54" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="55">
@@ -14066,10 +14066,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G55" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="56">
@@ -14092,10 +14092,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G56" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="57">
@@ -14118,10 +14118,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G57" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="58">
@@ -14144,10 +14144,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G58" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="59">
@@ -14170,10 +14170,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G59" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="60">
@@ -14199,7 +14199,7 @@
         <v>1ms</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="61">
@@ -14222,10 +14222,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G61" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="62">
@@ -14248,10 +14248,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G62" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="63">
@@ -14277,7 +14277,7 @@
         <v>1ms</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="64">
@@ -14303,7 +14303,7 @@
         <v>1ms</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="65">
@@ -14329,7 +14329,7 @@
         <v>4ms</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="66">
@@ -14352,10 +14352,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G66" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="67">
@@ -14378,10 +14378,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G67" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="68">
@@ -14404,10 +14404,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G68" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="69">
@@ -14430,10 +14430,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G69" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="70">
@@ -14456,10 +14456,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G70" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="71">
@@ -14482,10 +14482,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G71" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="72">
@@ -14508,10 +14508,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G72" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="73">
@@ -14534,10 +14534,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G73" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="74">
@@ -14560,10 +14560,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G74" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="75">
@@ -14589,7 +14589,7 @@
         <v>2ms</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
     <row r="76">
@@ -14612,10 +14612,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G76" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-28T07:18:44.997Z</v>
+        <v>2026-08-28T07:41:28.226Z</v>
       </c>
     </row>
   </sheetData>
@@ -14688,7 +14688,7 @@
         <v>3ms</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="3">
@@ -14711,10 +14711,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G3" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="4">
@@ -14740,7 +14740,7 @@
         <v>3ms</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="5">
@@ -14763,10 +14763,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G5" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="6">
@@ -14789,10 +14789,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G6" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="7">
@@ -14818,7 +14818,7 @@
         <v>2ms</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="8">
@@ -14844,7 +14844,7 @@
         <v>4ms</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="9">
@@ -14867,10 +14867,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G9" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="10">
@@ -14896,7 +14896,7 @@
         <v>1ms</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="11">
@@ -14919,10 +14919,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G11" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="12">
@@ -14948,7 +14948,7 @@
         <v>3ms</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="13">
@@ -14971,10 +14971,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G13" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="14">
@@ -15000,7 +15000,7 @@
         <v>3ms</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="15">
@@ -15023,10 +15023,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G15" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="16">
@@ -15049,10 +15049,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G16" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="17">
@@ -15075,10 +15075,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G17" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="18">
@@ -15101,10 +15101,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G18" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="19">
@@ -15130,7 +15130,7 @@
         <v>4ms</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="20">
@@ -15153,10 +15153,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G20" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="21">
@@ -15179,10 +15179,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G21" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="22">
@@ -15205,10 +15205,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G22" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="23">
@@ -15231,10 +15231,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G23" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="24">
@@ -15257,10 +15257,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G24" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="25">
@@ -15283,10 +15283,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G25" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="26">
@@ -15309,10 +15309,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G26" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="27">
@@ -15335,10 +15335,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G27" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="28">
@@ -15364,7 +15364,7 @@
         <v>1ms</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="29">
@@ -15387,10 +15387,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G29" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="30">
@@ -15416,7 +15416,7 @@
         <v>3ms</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="31">
@@ -15442,7 +15442,7 @@
         <v>4ms</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="32">
@@ -15468,7 +15468,7 @@
         <v>2ms</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="33">
@@ -15491,10 +15491,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G33" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="34">
@@ -15517,10 +15517,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G34" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="35">
@@ -15546,7 +15546,7 @@
         <v>1ms</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="36">
@@ -15569,10 +15569,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G36" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="37">
@@ -15598,7 +15598,7 @@
         <v>2ms</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="38">
@@ -15624,7 +15624,7 @@
         <v>3ms</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="39">
@@ -15647,10 +15647,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G39" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="40">
@@ -15673,10 +15673,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G40" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="41">
@@ -15699,10 +15699,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G41" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="42">
@@ -15725,10 +15725,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G42" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="43">
@@ -15751,10 +15751,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G43" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="44">
@@ -15777,10 +15777,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G44" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="45">
@@ -15803,10 +15803,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G45" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="46">
@@ -15829,10 +15829,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G46" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="47">
@@ -15855,10 +15855,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G47" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="48">
@@ -15881,10 +15881,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G48" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="49">
@@ -15910,7 +15910,7 @@
         <v>1ms</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="50">
@@ -15933,10 +15933,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G50" t="str">
-        <v>4ms</v>
+        <v>3ms</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="51">
@@ -15959,10 +15959,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G51" t="str">
-        <v>4ms</v>
+        <v>1ms</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="52">
@@ -15985,10 +15985,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G52" t="str">
-        <v>4ms</v>
+        <v>2ms</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="53">
@@ -16014,7 +16014,7 @@
         <v>4ms</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="54">
@@ -16037,10 +16037,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G54" t="str">
-        <v>1ms</v>
+        <v>4ms</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="55">
@@ -16063,10 +16063,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G55" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="56">
@@ -16089,10 +16089,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G56" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="57">
@@ -16118,7 +16118,7 @@
         <v>2ms</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="58">
@@ -16144,7 +16144,7 @@
         <v>4ms</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="59">
@@ -16170,7 +16170,7 @@
         <v>2ms</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="60">
@@ -16193,10 +16193,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G60" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="61">
@@ -16222,7 +16222,7 @@
         <v>4ms</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="62">
@@ -16245,10 +16245,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G62" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="63">
@@ -16271,10 +16271,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G63" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="64">
@@ -16297,10 +16297,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G64" t="str">
-        <v>3ms</v>
+        <v>1ms</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="65">
@@ -16326,7 +16326,7 @@
         <v>4ms</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="66">
@@ -16352,7 +16352,7 @@
         <v>1ms</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.227Z</v>
       </c>
     </row>
     <row r="67">
@@ -16378,7 +16378,7 @@
         <v>2ms</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="68">
@@ -16401,10 +16401,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G68" t="str">
-        <v>3ms</v>
+        <v>4ms</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="69">
@@ -16427,10 +16427,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G69" t="str">
-        <v>1ms</v>
+        <v>2ms</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="70">
@@ -16453,10 +16453,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G70" t="str">
-        <v>2ms</v>
+        <v>3ms</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="71">
@@ -16479,10 +16479,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G71" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="72">
@@ -16505,10 +16505,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G72" t="str">
-        <v>1ms</v>
+        <v>3ms</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="73">
@@ -16531,10 +16531,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G73" t="str">
-        <v>2ms</v>
+        <v>1ms</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="74">
@@ -16560,7 +16560,7 @@
         <v>3ms</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-28T07:18:44.998Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="75">
@@ -16583,10 +16583,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G75" t="str">
-        <v>2ms</v>
+        <v>4ms</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-28T07:18:44.999Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
     <row r="76">
@@ -16609,10 +16609,10 @@
         <v>Vitest v4.1 (V8)</v>
       </c>
       <c r="G76" t="str">
-        <v>3ms</v>
+        <v>2ms</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-28T07:18:44.999Z</v>
+        <v>2026-08-28T07:41:28.228Z</v>
       </c>
     </row>
   </sheetData>
